--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751719</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129751740</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129751704</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129751737</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129751728</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751699</v>
+        <v>129751730</v>
       </c>
       <c r="B7" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,42 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463848</v>
+        <v>463760</v>
       </c>
       <c r="R7" t="n">
-        <v>7057352</v>
+        <v>7057294</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,7 +1260,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751730</v>
+        <v>129751699</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,34 +1298,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463760</v>
+        <v>463848</v>
       </c>
       <c r="R8" t="n">
-        <v>7057294</v>
+        <v>7057352</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,7 +1400,7 @@
         <v>129751712</v>
       </c>
       <c r="B9" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751705</v>
+        <v>129751755</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>88987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463881</v>
+        <v>463778</v>
       </c>
       <c r="R10" t="n">
-        <v>7057240</v>
+        <v>7057403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,7 +1590,7 @@
         <v>129751718</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751755</v>
+        <v>129751709</v>
       </c>
       <c r="B12" t="n">
-        <v>88986</v>
+        <v>80181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1729,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463778</v>
+        <v>463921</v>
       </c>
       <c r="R12" t="n">
-        <v>7057403</v>
+        <v>7057254</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751709</v>
+        <v>129751705</v>
       </c>
       <c r="B13" t="n">
-        <v>80180</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463921</v>
+        <v>463881</v>
       </c>
       <c r="R13" t="n">
-        <v>7057254</v>
+        <v>7057240</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,6 +1857,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,7 +1891,7 @@
         <v>129751734</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>129751729</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129751736</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>129751698</v>
       </c>
       <c r="B17" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>129751739</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129751733</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>129751735</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>129751711</v>
       </c>
       <c r="B21" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>129751722</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>129751738</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>129751720</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>129751732</v>
       </c>
       <c r="B25" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>129751717</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>129751713</v>
       </c>
       <c r="B27" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>129751716</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>129751731</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>129751749</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>129751714</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>129751757</v>
       </c>
       <c r="B32" t="n">
-        <v>88986</v>
+        <v>88987</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>129751750</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>129751752</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>129751727</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>129751724</v>
       </c>
       <c r="B36" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129751753</v>
       </c>
       <c r="B37" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>129751745</v>
       </c>
       <c r="B38" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>129751726</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>129751751</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>129751742</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>129751725</v>
       </c>
       <c r="B42" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>129751743</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>129751754</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>129751710</v>
       </c>
       <c r="B45" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129751700</v>
+        <v>129751715</v>
       </c>
       <c r="B46" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463923</v>
+        <v>463874</v>
       </c>
       <c r="R46" t="n">
-        <v>7057789</v>
+        <v>7057530</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5216,10 +5216,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129751715</v>
+        <v>129751700</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5227,21 +5227,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463874</v>
+        <v>463923</v>
       </c>
       <c r="R47" t="n">
-        <v>7057530</v>
+        <v>7057789</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5321,7 +5321,7 @@
         <v>129751741</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>129751703</v>
       </c>
       <c r="B49" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>129751756</v>
       </c>
       <c r="B50" t="n">
-        <v>88986</v>
+        <v>88987</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>129751748</v>
       </c>
       <c r="B51" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>129751747</v>
       </c>
       <c r="B52" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5823,10 +5823,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129751723</v>
+        <v>129751701</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463838</v>
+        <v>463931</v>
       </c>
       <c r="R53" t="n">
-        <v>7057454</v>
+        <v>7057799</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751701</v>
+        <v>129751723</v>
       </c>
       <c r="B54" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463931</v>
+        <v>463838</v>
       </c>
       <c r="R54" t="n">
-        <v>7057799</v>
+        <v>7057454</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6030,7 +6030,7 @@
         <v>129751707</v>
       </c>
       <c r="B55" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -3497,10 +3497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751749</v>
+        <v>129751757</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>88987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,21 +3508,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463943</v>
+        <v>463874</v>
       </c>
       <c r="R30" t="n">
-        <v>7057664</v>
+        <v>7057476</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,11 +3568,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3599,7 +3594,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751714</v>
+        <v>129751749</v>
       </c>
       <c r="B31" t="n">
         <v>79076</v>
@@ -3634,10 +3629,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463852</v>
+        <v>463943</v>
       </c>
       <c r="R31" t="n">
-        <v>7057546</v>
+        <v>7057664</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3674,7 +3669,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3701,10 +3696,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751757</v>
+        <v>129751714</v>
       </c>
       <c r="B32" t="n">
-        <v>88987</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3712,21 +3707,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3736,10 +3731,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463874</v>
+        <v>463852</v>
       </c>
       <c r="R32" t="n">
-        <v>7057476</v>
+        <v>7057546</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,6 +3767,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5823,10 +5823,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129751701</v>
+        <v>129751723</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>79076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463931</v>
+        <v>463838</v>
       </c>
       <c r="R53" t="n">
-        <v>7057799</v>
+        <v>7057454</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751723</v>
+        <v>129751701</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463838</v>
+        <v>463931</v>
       </c>
       <c r="R54" t="n">
-        <v>7057454</v>
+        <v>7057799</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751719</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129751740</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129751737</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129751728</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751730</v>
+        <v>129751712</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>91613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,23 +1196,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1220,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463760</v>
+        <v>463850</v>
       </c>
       <c r="R7" t="n">
-        <v>7057294</v>
+        <v>7057352</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,11 +1252,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751712</v>
+        <v>129751730</v>
       </c>
       <c r="B9" t="n">
-        <v>91608</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,19 +1399,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1428,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463850</v>
+        <v>463760</v>
       </c>
       <c r="R9" t="n">
-        <v>7057352</v>
+        <v>7057294</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,6 +1459,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,7 +1493,7 @@
         <v>129751755</v>
       </c>
       <c r="B10" t="n">
-        <v>88987</v>
+        <v>88992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751718</v>
+        <v>129751705</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,21 +1598,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463790</v>
+        <v>463881</v>
       </c>
       <c r="R11" t="n">
-        <v>7057272</v>
+        <v>7057240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751709</v>
+        <v>129751718</v>
       </c>
       <c r="B12" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463921</v>
+        <v>463790</v>
       </c>
       <c r="R12" t="n">
-        <v>7057254</v>
+        <v>7057272</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,6 +1760,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751705</v>
+        <v>129751709</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463881</v>
+        <v>463921</v>
       </c>
       <c r="R13" t="n">
-        <v>7057240</v>
+        <v>7057254</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,11 +1862,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,7 +1891,7 @@
         <v>129751734</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>129751729</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129751736</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>129751698</v>
       </c>
       <c r="B17" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>129751739</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129751733</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>129751735</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>129751711</v>
       </c>
       <c r="B21" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>129751722</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>129751738</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>129751720</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>129751732</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>129751717</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129751713</v>
+        <v>129751716</v>
       </c>
       <c r="B27" t="n">
-        <v>91608</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3211,19 +3211,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3231,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463871</v>
+        <v>463820</v>
       </c>
       <c r="R27" t="n">
-        <v>7057401</v>
+        <v>7057388</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3267,6 +3271,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3293,10 +3302,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129751716</v>
+        <v>129751731</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3328,10 +3337,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463820</v>
+        <v>463755</v>
       </c>
       <c r="R28" t="n">
-        <v>7057388</v>
+        <v>7057263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,7 +3377,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3395,10 +3404,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751731</v>
+        <v>129751713</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>91613</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,23 +3415,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3430,10 +3435,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463755</v>
+        <v>463871</v>
       </c>
       <c r="R29" t="n">
-        <v>7057263</v>
+        <v>7057401</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3466,11 +3471,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3500,7 +3500,7 @@
         <v>129751757</v>
       </c>
       <c r="B30" t="n">
-        <v>88987</v>
+        <v>88992</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>129751749</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>129751714</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>129751750</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>129751752</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>129751727</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4104,10 +4104,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129751724</v>
+        <v>129751753</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463856</v>
+        <v>463989</v>
       </c>
       <c r="R36" t="n">
-        <v>7057496</v>
+        <v>7057802</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129751753</v>
+        <v>129751745</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463989</v>
+        <v>463911</v>
       </c>
       <c r="R37" t="n">
-        <v>7057802</v>
+        <v>7057496</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4308,10 +4308,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129751745</v>
+        <v>129751724</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463911</v>
+        <v>463856</v>
       </c>
       <c r="R38" t="n">
         <v>7057496</v>
@@ -4413,7 +4413,7 @@
         <v>129751726</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>129751751</v>
       </c>
       <c r="B40" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>129751742</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>129751725</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>129751743</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>129751754</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>129751715</v>
       </c>
       <c r="B46" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>129751741</v>
       </c>
       <c r="B48" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>129751756</v>
       </c>
       <c r="B50" t="n">
-        <v>88987</v>
+        <v>88992</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5619,10 +5619,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129751748</v>
+        <v>129751747</v>
       </c>
       <c r="B51" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>463928</v>
+        <v>463926</v>
       </c>
       <c r="R51" t="n">
-        <v>7057569</v>
+        <v>7057553</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5721,10 +5721,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129751747</v>
+        <v>129751748</v>
       </c>
       <c r="B52" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>463926</v>
+        <v>463928</v>
       </c>
       <c r="R52" t="n">
-        <v>7057553</v>
+        <v>7057569</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5823,10 +5823,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129751723</v>
+        <v>129751701</v>
       </c>
       <c r="B53" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463838</v>
+        <v>463931</v>
       </c>
       <c r="R53" t="n">
-        <v>7057454</v>
+        <v>7057799</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751701</v>
+        <v>129751723</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463931</v>
+        <v>463838</v>
       </c>
       <c r="R54" t="n">
-        <v>7057799</v>
+        <v>7057454</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751755</v>
+        <v>129751705</v>
       </c>
       <c r="B10" t="n">
-        <v>88992</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463778</v>
+        <v>463881</v>
       </c>
       <c r="R10" t="n">
-        <v>7057403</v>
+        <v>7057240</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,6 +1561,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751705</v>
+        <v>129751709</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,21 +1603,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463881</v>
+        <v>463921</v>
       </c>
       <c r="R11" t="n">
-        <v>7057240</v>
+        <v>7057254</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,11 +1663,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751709</v>
+        <v>129751755</v>
       </c>
       <c r="B13" t="n">
-        <v>80186</v>
+        <v>88992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463921</v>
+        <v>463778</v>
       </c>
       <c r="R13" t="n">
-        <v>7057254</v>
+        <v>7057403</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129751716</v>
+        <v>129751713</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3211,23 +3211,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3235,10 +3231,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463820</v>
+        <v>463871</v>
       </c>
       <c r="R27" t="n">
-        <v>7057388</v>
+        <v>7057401</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3271,11 +3267,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3302,7 +3293,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129751731</v>
+        <v>129751716</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3337,10 +3328,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463755</v>
+        <v>463820</v>
       </c>
       <c r="R28" t="n">
-        <v>7057263</v>
+        <v>7057388</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3377,7 +3368,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3404,10 +3395,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751713</v>
+        <v>129751731</v>
       </c>
       <c r="B29" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,19 +3406,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3435,10 +3430,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463871</v>
+        <v>463755</v>
       </c>
       <c r="R29" t="n">
-        <v>7057401</v>
+        <v>7057263</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3471,6 +3466,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3497,10 +3497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751757</v>
+        <v>129751749</v>
       </c>
       <c r="B30" t="n">
-        <v>88992</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,21 +3508,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463874</v>
+        <v>463943</v>
       </c>
       <c r="R30" t="n">
-        <v>7057476</v>
+        <v>7057664</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,6 +3568,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3594,7 +3599,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751749</v>
+        <v>129751714</v>
       </c>
       <c r="B31" t="n">
         <v>79081</v>
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463943</v>
+        <v>463852</v>
       </c>
       <c r="R31" t="n">
-        <v>7057664</v>
+        <v>7057546</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3669,7 +3674,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3696,10 +3701,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751714</v>
+        <v>129751757</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>88992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3707,21 +3712,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3731,10 +3736,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463852</v>
+        <v>463874</v>
       </c>
       <c r="R32" t="n">
-        <v>7057546</v>
+        <v>7057476</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3767,11 +3772,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4818,7 +4818,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129751743</v>
+        <v>129751754</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463870</v>
+        <v>464011</v>
       </c>
       <c r="R43" t="n">
-        <v>7057473</v>
+        <v>7057803</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4889,11 +4889,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4920,7 +4915,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129751754</v>
+        <v>129751743</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -4955,10 +4950,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464011</v>
+        <v>463870</v>
       </c>
       <c r="R44" t="n">
-        <v>7057803</v>
+        <v>7057473</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4991,6 +4986,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5114,10 +5114,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129751715</v>
+        <v>129751700</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463874</v>
+        <v>463923</v>
       </c>
       <c r="R46" t="n">
-        <v>7057530</v>
+        <v>7057789</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5216,10 +5216,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129751700</v>
+        <v>129751715</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5227,21 +5227,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463923</v>
+        <v>463874</v>
       </c>
       <c r="R47" t="n">
-        <v>7057789</v>
+        <v>7057530</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5619,7 +5619,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129751747</v>
+        <v>129751748</v>
       </c>
       <c r="B51" t="n">
         <v>79081</v>
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>463926</v>
+        <v>463928</v>
       </c>
       <c r="R51" t="n">
-        <v>7057553</v>
+        <v>7057569</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5721,7 +5721,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129751748</v>
+        <v>129751747</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>463928</v>
+        <v>463926</v>
       </c>
       <c r="R52" t="n">
-        <v>7057569</v>
+        <v>7057553</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5823,10 +5823,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129751701</v>
+        <v>129751723</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463931</v>
+        <v>463838</v>
       </c>
       <c r="R53" t="n">
-        <v>7057799</v>
+        <v>7057454</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751723</v>
+        <v>129751701</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463838</v>
+        <v>463931</v>
       </c>
       <c r="R54" t="n">
-        <v>7057454</v>
+        <v>7057799</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751712</v>
+        <v>129751730</v>
       </c>
       <c r="B7" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,19 +1196,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1216,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463850</v>
+        <v>463760</v>
       </c>
       <c r="R7" t="n">
-        <v>7057352</v>
+        <v>7057294</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,6 +1256,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1278,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751699</v>
+        <v>129751712</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,39 +1298,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463848</v>
+        <v>463850</v>
       </c>
       <c r="R8" t="n">
         <v>7057352</v>
@@ -1357,11 +1354,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751730</v>
+        <v>129751699</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,34 +1391,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463760</v>
+        <v>463848</v>
       </c>
       <c r="R9" t="n">
-        <v>7057294</v>
+        <v>7057352</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751705</v>
+        <v>129751755</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>88992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463881</v>
+        <v>463778</v>
       </c>
       <c r="R10" t="n">
-        <v>7057240</v>
+        <v>7057403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,10 +1587,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751709</v>
+        <v>129751718</v>
       </c>
       <c r="B11" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,21 +1598,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463921</v>
+        <v>463790</v>
       </c>
       <c r="R11" t="n">
-        <v>7057254</v>
+        <v>7057272</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,6 +1658,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751718</v>
+        <v>129751709</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463790</v>
+        <v>463921</v>
       </c>
       <c r="R12" t="n">
-        <v>7057272</v>
+        <v>7057254</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,11 +1760,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751755</v>
+        <v>129751705</v>
       </c>
       <c r="B13" t="n">
-        <v>88992</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463778</v>
+        <v>463881</v>
       </c>
       <c r="R13" t="n">
-        <v>7057403</v>
+        <v>7057240</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,6 +1857,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2792,7 +2792,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129751738</v>
+        <v>129751720</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463940</v>
+        <v>463816</v>
       </c>
       <c r="R23" t="n">
-        <v>7057328</v>
+        <v>7057325</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2894,7 +2894,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751720</v>
+        <v>129751732</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463816</v>
+        <v>463782</v>
       </c>
       <c r="R24" t="n">
-        <v>7057325</v>
+        <v>7057216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,7 +2996,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751732</v>
+        <v>129751738</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463782</v>
+        <v>463940</v>
       </c>
       <c r="R25" t="n">
-        <v>7057216</v>
+        <v>7057328</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129751713</v>
+        <v>129751716</v>
       </c>
       <c r="B27" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3211,19 +3211,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3231,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463871</v>
+        <v>463820</v>
       </c>
       <c r="R27" t="n">
-        <v>7057401</v>
+        <v>7057388</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3267,6 +3271,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3293,7 +3302,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129751716</v>
+        <v>129751731</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3328,10 +3337,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463820</v>
+        <v>463755</v>
       </c>
       <c r="R28" t="n">
-        <v>7057388</v>
+        <v>7057263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,7 +3377,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3395,10 +3404,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751731</v>
+        <v>129751713</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,23 +3415,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3430,10 +3435,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463755</v>
+        <v>463871</v>
       </c>
       <c r="R29" t="n">
-        <v>7057263</v>
+        <v>7057401</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3466,11 +3471,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3497,10 +3497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751749</v>
+        <v>129751757</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>88992</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,21 +3508,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463943</v>
+        <v>463874</v>
       </c>
       <c r="R30" t="n">
-        <v>7057664</v>
+        <v>7057476</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,11 +3568,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3599,7 +3594,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751714</v>
+        <v>129751749</v>
       </c>
       <c r="B31" t="n">
         <v>79081</v>
@@ -3634,10 +3629,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463852</v>
+        <v>463943</v>
       </c>
       <c r="R31" t="n">
-        <v>7057546</v>
+        <v>7057664</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3674,7 +3669,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3701,10 +3696,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751757</v>
+        <v>129751714</v>
       </c>
       <c r="B32" t="n">
-        <v>88992</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3712,21 +3707,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3736,10 +3731,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463874</v>
+        <v>463852</v>
       </c>
       <c r="R32" t="n">
-        <v>7057476</v>
+        <v>7057546</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,6 +3767,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4104,7 +4104,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129751753</v>
+        <v>129751724</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463989</v>
+        <v>463856</v>
       </c>
       <c r="R36" t="n">
-        <v>7057802</v>
+        <v>7057496</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4206,7 +4206,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129751745</v>
+        <v>129751753</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463911</v>
+        <v>463989</v>
       </c>
       <c r="R37" t="n">
-        <v>7057496</v>
+        <v>7057802</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4308,7 +4308,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129751724</v>
+        <v>129751745</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463856</v>
+        <v>463911</v>
       </c>
       <c r="R38" t="n">
         <v>7057496</v>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129751700</v>
+        <v>129751715</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463923</v>
+        <v>463874</v>
       </c>
       <c r="R46" t="n">
-        <v>7057789</v>
+        <v>7057530</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5216,10 +5216,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129751715</v>
+        <v>129751700</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5227,21 +5227,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463874</v>
+        <v>463923</v>
       </c>
       <c r="R47" t="n">
-        <v>7057530</v>
+        <v>7057789</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5823,10 +5823,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129751723</v>
+        <v>129751701</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463838</v>
+        <v>463931</v>
       </c>
       <c r="R53" t="n">
-        <v>7057454</v>
+        <v>7057799</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751701</v>
+        <v>129751723</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463931</v>
+        <v>463838</v>
       </c>
       <c r="R54" t="n">
-        <v>7057799</v>
+        <v>7057454</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751730</v>
+        <v>129751712</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,23 +1196,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1220,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463760</v>
+        <v>463850</v>
       </c>
       <c r="R7" t="n">
-        <v>7057294</v>
+        <v>7057352</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,11 +1252,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751712</v>
+        <v>129751730</v>
       </c>
       <c r="B8" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,19 +1289,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1318,10 +1313,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463850</v>
+        <v>463760</v>
       </c>
       <c r="R8" t="n">
-        <v>7057352</v>
+        <v>7057294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,6 +1349,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751755</v>
+        <v>129751718</v>
       </c>
       <c r="B10" t="n">
-        <v>88992</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463778</v>
+        <v>463790</v>
       </c>
       <c r="R10" t="n">
-        <v>7057403</v>
+        <v>7057272</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,6 +1561,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751718</v>
+        <v>129751709</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,21 +1603,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463790</v>
+        <v>463921</v>
       </c>
       <c r="R11" t="n">
-        <v>7057272</v>
+        <v>7057254</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,11 +1663,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751709</v>
+        <v>129751705</v>
       </c>
       <c r="B12" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463921</v>
+        <v>463881</v>
       </c>
       <c r="R12" t="n">
-        <v>7057254</v>
+        <v>7057240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,6 +1760,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751705</v>
+        <v>129751755</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>88992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463881</v>
+        <v>463778</v>
       </c>
       <c r="R13" t="n">
-        <v>7057240</v>
+        <v>7057403</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,11 +1862,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2792,7 +2792,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129751720</v>
+        <v>129751738</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463816</v>
+        <v>463940</v>
       </c>
       <c r="R23" t="n">
-        <v>7057325</v>
+        <v>7057328</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2894,7 +2894,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751732</v>
+        <v>129751720</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463782</v>
+        <v>463816</v>
       </c>
       <c r="R24" t="n">
-        <v>7057216</v>
+        <v>7057325</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,7 +2996,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751738</v>
+        <v>129751732</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463940</v>
+        <v>463782</v>
       </c>
       <c r="R25" t="n">
-        <v>7057328</v>
+        <v>7057216</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129751716</v>
+        <v>129751713</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3211,23 +3211,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3235,10 +3231,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463820</v>
+        <v>463871</v>
       </c>
       <c r="R27" t="n">
-        <v>7057388</v>
+        <v>7057401</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3271,11 +3267,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3302,7 +3293,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129751731</v>
+        <v>129751716</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3337,10 +3328,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463755</v>
+        <v>463820</v>
       </c>
       <c r="R28" t="n">
-        <v>7057263</v>
+        <v>7057388</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3377,7 +3368,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3404,10 +3395,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751713</v>
+        <v>129751731</v>
       </c>
       <c r="B29" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,19 +3406,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3435,10 +3430,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463871</v>
+        <v>463755</v>
       </c>
       <c r="R29" t="n">
-        <v>7057401</v>
+        <v>7057263</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3471,6 +3466,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4818,7 +4818,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129751754</v>
+        <v>129751743</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464011</v>
+        <v>463870</v>
       </c>
       <c r="R43" t="n">
-        <v>7057803</v>
+        <v>7057473</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4889,6 +4889,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4915,7 +4920,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129751743</v>
+        <v>129751754</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -4950,10 +4955,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>463870</v>
+        <v>464011</v>
       </c>
       <c r="R44" t="n">
-        <v>7057473</v>
+        <v>7057803</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4986,11 +4991,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5823,10 +5823,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129751701</v>
+        <v>129751723</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463931</v>
+        <v>463838</v>
       </c>
       <c r="R53" t="n">
-        <v>7057799</v>
+        <v>7057454</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751723</v>
+        <v>129751701</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463838</v>
+        <v>463931</v>
       </c>
       <c r="R54" t="n">
-        <v>7057454</v>
+        <v>7057799</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>129751712</v>
       </c>
       <c r="B7" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751730</v>
+        <v>129751699</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,34 +1289,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463760</v>
+        <v>463848</v>
       </c>
       <c r="R8" t="n">
-        <v>7057294</v>
+        <v>7057352</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,7 +1361,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751699</v>
+        <v>129751730</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,42 +1399,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463848</v>
+        <v>463760</v>
       </c>
       <c r="R9" t="n">
-        <v>7057352</v>
+        <v>7057294</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751718</v>
+        <v>129751755</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>88996</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463790</v>
+        <v>463778</v>
       </c>
       <c r="R10" t="n">
-        <v>7057272</v>
+        <v>7057403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1791,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751755</v>
+        <v>129751718</v>
       </c>
       <c r="B13" t="n">
-        <v>88992</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463778</v>
+        <v>463790</v>
       </c>
       <c r="R13" t="n">
-        <v>7057403</v>
+        <v>7057272</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,6 +1857,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2197,7 +2197,7 @@
         <v>129751698</v>
       </c>
       <c r="B17" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129751739</v>
+        <v>129751735</v>
       </c>
       <c r="B18" t="n">
         <v>79081</v>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463878</v>
+        <v>463867</v>
       </c>
       <c r="R18" t="n">
-        <v>7057324</v>
+        <v>7057230</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2495,7 +2495,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129751735</v>
+        <v>129751739</v>
       </c>
       <c r="B20" t="n">
         <v>79081</v>
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463867</v>
+        <v>463878</v>
       </c>
       <c r="R20" t="n">
-        <v>7057230</v>
+        <v>7057324</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2600,7 +2600,7 @@
         <v>129751711</v>
       </c>
       <c r="B21" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129751738</v>
+        <v>129751732</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463940</v>
+        <v>463782</v>
       </c>
       <c r="R23" t="n">
-        <v>7057328</v>
+        <v>7057216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2996,7 +2996,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751732</v>
+        <v>129751738</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463782</v>
+        <v>463940</v>
       </c>
       <c r="R25" t="n">
-        <v>7057216</v>
+        <v>7057328</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,7 +3203,7 @@
         <v>129751713</v>
       </c>
       <c r="B27" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129751716</v>
+        <v>129751731</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463820</v>
+        <v>463755</v>
       </c>
       <c r="R28" t="n">
-        <v>7057388</v>
+        <v>7057263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3395,7 +3395,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751731</v>
+        <v>129751716</v>
       </c>
       <c r="B29" t="n">
         <v>79081</v>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463755</v>
+        <v>463820</v>
       </c>
       <c r="R29" t="n">
-        <v>7057263</v>
+        <v>7057388</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3500,7 +3500,7 @@
         <v>129751757</v>
       </c>
       <c r="B30" t="n">
-        <v>88992</v>
+        <v>88996</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751749</v>
+        <v>129751714</v>
       </c>
       <c r="B31" t="n">
         <v>79081</v>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463943</v>
+        <v>463852</v>
       </c>
       <c r="R31" t="n">
-        <v>7057664</v>
+        <v>7057546</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3696,7 +3696,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751714</v>
+        <v>129751749</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463852</v>
+        <v>463943</v>
       </c>
       <c r="R32" t="n">
-        <v>7057546</v>
+        <v>7057664</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4104,7 +4104,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129751724</v>
+        <v>129751753</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463856</v>
+        <v>463989</v>
       </c>
       <c r="R36" t="n">
-        <v>7057496</v>
+        <v>7057802</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4206,7 +4206,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129751753</v>
+        <v>129751745</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463989</v>
+        <v>463911</v>
       </c>
       <c r="R37" t="n">
-        <v>7057802</v>
+        <v>7057496</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4308,7 +4308,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129751745</v>
+        <v>129751724</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463911</v>
+        <v>463856</v>
       </c>
       <c r="R38" t="n">
         <v>7057496</v>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129751715</v>
+        <v>129751700</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463874</v>
+        <v>463923</v>
       </c>
       <c r="R46" t="n">
-        <v>7057530</v>
+        <v>7057789</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5216,10 +5216,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129751700</v>
+        <v>129751715</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5227,21 +5227,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463923</v>
+        <v>463874</v>
       </c>
       <c r="R47" t="n">
-        <v>7057789</v>
+        <v>7057530</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5525,7 +5525,7 @@
         <v>129751756</v>
       </c>
       <c r="B50" t="n">
-        <v>88992</v>
+        <v>88996</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129751748</v>
+        <v>129751747</v>
       </c>
       <c r="B51" t="n">
         <v>79081</v>
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>463928</v>
+        <v>463926</v>
       </c>
       <c r="R51" t="n">
-        <v>7057569</v>
+        <v>7057553</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5721,7 +5721,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129751747</v>
+        <v>129751748</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>463926</v>
+        <v>463928</v>
       </c>
       <c r="R52" t="n">
-        <v>7057553</v>
+        <v>7057569</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5823,10 +5823,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129751723</v>
+        <v>129751701</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463838</v>
+        <v>463931</v>
       </c>
       <c r="R53" t="n">
-        <v>7057454</v>
+        <v>7057799</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751701</v>
+        <v>129751723</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463931</v>
+        <v>463838</v>
       </c>
       <c r="R54" t="n">
-        <v>7057799</v>
+        <v>7057454</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>129751712</v>
       </c>
       <c r="B7" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751699</v>
+        <v>129751730</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,42 +1289,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463848</v>
+        <v>463760</v>
       </c>
       <c r="R8" t="n">
-        <v>7057352</v>
+        <v>7057294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,7 +1353,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751730</v>
+        <v>129751699</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,34 +1391,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463760</v>
+        <v>463848</v>
       </c>
       <c r="R9" t="n">
-        <v>7057294</v>
+        <v>7057352</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751755</v>
+        <v>129751718</v>
       </c>
       <c r="B10" t="n">
-        <v>88996</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463778</v>
+        <v>463790</v>
       </c>
       <c r="R10" t="n">
-        <v>7057403</v>
+        <v>7057272</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,6 +1561,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751705</v>
+        <v>129751755</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>88998</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1719,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463881</v>
+        <v>463778</v>
       </c>
       <c r="R12" t="n">
-        <v>7057240</v>
+        <v>7057403</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,11 +1760,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751718</v>
+        <v>129751705</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463790</v>
+        <v>463881</v>
       </c>
       <c r="R13" t="n">
-        <v>7057272</v>
+        <v>7057240</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2197,7 +2197,7 @@
         <v>129751698</v>
       </c>
       <c r="B17" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>129751711</v>
       </c>
       <c r="B21" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>129751713</v>
       </c>
       <c r="B27" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751757</v>
+        <v>129751714</v>
       </c>
       <c r="B30" t="n">
-        <v>88996</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,21 +3508,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463874</v>
+        <v>463852</v>
       </c>
       <c r="R30" t="n">
-        <v>7057476</v>
+        <v>7057546</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,6 +3568,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3594,7 +3599,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751714</v>
+        <v>129751749</v>
       </c>
       <c r="B31" t="n">
         <v>79081</v>
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463852</v>
+        <v>463943</v>
       </c>
       <c r="R31" t="n">
-        <v>7057546</v>
+        <v>7057664</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3669,7 +3674,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3696,10 +3701,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751749</v>
+        <v>129751757</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>88998</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3707,21 +3712,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3731,10 +3736,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463943</v>
+        <v>463874</v>
       </c>
       <c r="R32" t="n">
-        <v>7057664</v>
+        <v>7057476</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3767,11 +3772,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5114,10 +5114,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129751700</v>
+        <v>129751715</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463923</v>
+        <v>463874</v>
       </c>
       <c r="R46" t="n">
-        <v>7057789</v>
+        <v>7057530</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5216,10 +5216,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129751715</v>
+        <v>129751700</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5227,21 +5227,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463874</v>
+        <v>463923</v>
       </c>
       <c r="R47" t="n">
-        <v>7057530</v>
+        <v>7057789</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5525,7 +5525,7 @@
         <v>129751756</v>
       </c>
       <c r="B50" t="n">
-        <v>88996</v>
+        <v>88998</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5823,10 +5823,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129751701</v>
+        <v>129751723</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463931</v>
+        <v>463838</v>
       </c>
       <c r="R53" t="n">
-        <v>7057799</v>
+        <v>7057454</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751723</v>
+        <v>129751701</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463838</v>
+        <v>463931</v>
       </c>
       <c r="R54" t="n">
-        <v>7057454</v>
+        <v>7057799</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -5114,10 +5114,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129751715</v>
+        <v>129751700</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463874</v>
+        <v>463923</v>
       </c>
       <c r="R46" t="n">
-        <v>7057530</v>
+        <v>7057789</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5216,10 +5216,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129751700</v>
+        <v>129751715</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5227,21 +5227,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463923</v>
+        <v>463874</v>
       </c>
       <c r="R47" t="n">
-        <v>7057789</v>
+        <v>7057530</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751718</v>
+        <v>129751755</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>88998</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463790</v>
+        <v>463778</v>
       </c>
       <c r="R10" t="n">
-        <v>7057272</v>
+        <v>7057403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,10 +1587,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751709</v>
+        <v>129751718</v>
       </c>
       <c r="B11" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,21 +1598,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463921</v>
+        <v>463790</v>
       </c>
       <c r="R11" t="n">
-        <v>7057254</v>
+        <v>7057272</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,6 +1658,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751755</v>
+        <v>129751709</v>
       </c>
       <c r="B12" t="n">
-        <v>88998</v>
+        <v>80186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463778</v>
+        <v>463921</v>
       </c>
       <c r="R12" t="n">
-        <v>7057403</v>
+        <v>7057254</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751755</v>
+        <v>129751705</v>
       </c>
       <c r="B10" t="n">
-        <v>88998</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463778</v>
+        <v>463881</v>
       </c>
       <c r="R10" t="n">
-        <v>7057403</v>
+        <v>7057240</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,6 +1561,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751718</v>
+        <v>129751755</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>88998</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,21 +1603,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463790</v>
+        <v>463778</v>
       </c>
       <c r="R11" t="n">
-        <v>7057272</v>
+        <v>7057403</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,11 +1663,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751709</v>
+        <v>129751718</v>
       </c>
       <c r="B12" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463921</v>
+        <v>463790</v>
       </c>
       <c r="R12" t="n">
-        <v>7057254</v>
+        <v>7057272</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,6 +1760,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751705</v>
+        <v>129751709</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463881</v>
+        <v>463921</v>
       </c>
       <c r="R13" t="n">
-        <v>7057240</v>
+        <v>7057254</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,11 +1862,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2291,7 +2291,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129751735</v>
+        <v>129751733</v>
       </c>
       <c r="B18" t="n">
         <v>79081</v>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463867</v>
+        <v>463805</v>
       </c>
       <c r="R18" t="n">
-        <v>7057230</v>
+        <v>7057194</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,7 +2393,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129751733</v>
+        <v>129751739</v>
       </c>
       <c r="B19" t="n">
         <v>79081</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463805</v>
+        <v>463878</v>
       </c>
       <c r="R19" t="n">
-        <v>7057194</v>
+        <v>7057324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2495,7 +2495,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129751739</v>
+        <v>129751735</v>
       </c>
       <c r="B20" t="n">
         <v>79081</v>
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463878</v>
+        <v>463867</v>
       </c>
       <c r="R20" t="n">
-        <v>7057324</v>
+        <v>7057230</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3293,7 +3293,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129751731</v>
+        <v>129751716</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463755</v>
+        <v>463820</v>
       </c>
       <c r="R28" t="n">
-        <v>7057263</v>
+        <v>7057388</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3395,7 +3395,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751716</v>
+        <v>129751731</v>
       </c>
       <c r="B29" t="n">
         <v>79081</v>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463820</v>
+        <v>463755</v>
       </c>
       <c r="R29" t="n">
-        <v>7057388</v>
+        <v>7057263</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3497,10 +3497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751714</v>
+        <v>129751757</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>88998</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,21 +3508,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463852</v>
+        <v>463874</v>
       </c>
       <c r="R30" t="n">
-        <v>7057546</v>
+        <v>7057476</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,11 +3568,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3701,10 +3696,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751757</v>
+        <v>129751714</v>
       </c>
       <c r="B32" t="n">
-        <v>88998</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3712,21 +3707,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3736,10 +3731,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463874</v>
+        <v>463852</v>
       </c>
       <c r="R32" t="n">
-        <v>7057476</v>
+        <v>7057546</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,6 +3767,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4410,7 +4410,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129751726</v>
+        <v>129751751</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463811</v>
+        <v>463918</v>
       </c>
       <c r="R39" t="n">
-        <v>7057478</v>
+        <v>7057725</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4512,7 +4512,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129751751</v>
+        <v>129751726</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463918</v>
+        <v>463811</v>
       </c>
       <c r="R40" t="n">
-        <v>7057725</v>
+        <v>7057478</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5114,10 +5114,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129751700</v>
+        <v>129751715</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463923</v>
+        <v>463874</v>
       </c>
       <c r="R46" t="n">
-        <v>7057789</v>
+        <v>7057530</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5216,10 +5216,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129751715</v>
+        <v>129751700</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5227,21 +5227,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463874</v>
+        <v>463923</v>
       </c>
       <c r="R47" t="n">
-        <v>7057530</v>
+        <v>7057789</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5619,7 +5619,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129751747</v>
+        <v>129751748</v>
       </c>
       <c r="B51" t="n">
         <v>79081</v>
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>463926</v>
+        <v>463928</v>
       </c>
       <c r="R51" t="n">
-        <v>7057553</v>
+        <v>7057569</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5721,7 +5721,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129751748</v>
+        <v>129751747</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>463928</v>
+        <v>463926</v>
       </c>
       <c r="R52" t="n">
-        <v>7057569</v>
+        <v>7057553</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5823,10 +5823,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129751723</v>
+        <v>129751701</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463838</v>
+        <v>463931</v>
       </c>
       <c r="R53" t="n">
-        <v>7057454</v>
+        <v>7057799</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751701</v>
+        <v>129751723</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463931</v>
+        <v>463838</v>
       </c>
       <c r="R54" t="n">
-        <v>7057799</v>
+        <v>7057454</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -2792,7 +2792,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129751732</v>
+        <v>129751738</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463782</v>
+        <v>463940</v>
       </c>
       <c r="R23" t="n">
-        <v>7057216</v>
+        <v>7057328</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2894,7 +2894,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751720</v>
+        <v>129751732</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463816</v>
+        <v>463782</v>
       </c>
       <c r="R24" t="n">
-        <v>7057325</v>
+        <v>7057216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,7 +2996,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751738</v>
+        <v>129751720</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463940</v>
+        <v>463816</v>
       </c>
       <c r="R25" t="n">
-        <v>7057328</v>
+        <v>7057325</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -5823,10 +5823,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129751701</v>
+        <v>129751723</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463931</v>
+        <v>463838</v>
       </c>
       <c r="R53" t="n">
-        <v>7057799</v>
+        <v>7057454</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751723</v>
+        <v>129751701</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463838</v>
+        <v>463931</v>
       </c>
       <c r="R54" t="n">
-        <v>7057454</v>
+        <v>7057799</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751719</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129751740</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129751704</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129751737</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129751728</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751712</v>
+        <v>129751730</v>
       </c>
       <c r="B7" t="n">
-        <v>91619</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,19 +1196,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1216,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463850</v>
+        <v>463760</v>
       </c>
       <c r="R7" t="n">
-        <v>7057352</v>
+        <v>7057294</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,6 +1256,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1278,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751730</v>
+        <v>129751712</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>91622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,23 +1298,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1313,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463760</v>
+        <v>463850</v>
       </c>
       <c r="R8" t="n">
-        <v>7057294</v>
+        <v>7057352</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1349,11 +1354,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1383,7 +1383,7 @@
         <v>129751699</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751705</v>
+        <v>129751709</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>80189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463881</v>
+        <v>463921</v>
       </c>
       <c r="R10" t="n">
-        <v>7057240</v>
+        <v>7057254</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,7 +1590,7 @@
         <v>129751755</v>
       </c>
       <c r="B11" t="n">
-        <v>88998</v>
+        <v>89001</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,10 +1684,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751718</v>
+        <v>129751705</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,21 +1695,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1719,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463790</v>
+        <v>463881</v>
       </c>
       <c r="R12" t="n">
-        <v>7057272</v>
+        <v>7057240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1764,7 +1759,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751709</v>
+        <v>129751718</v>
       </c>
       <c r="B13" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463921</v>
+        <v>463790</v>
       </c>
       <c r="R13" t="n">
-        <v>7057254</v>
+        <v>7057272</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,6 +1857,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,7 +1891,7 @@
         <v>129751734</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>129751729</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129751736</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>129751698</v>
       </c>
       <c r="B17" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129751733</v>
+        <v>129751739</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463805</v>
+        <v>463878</v>
       </c>
       <c r="R18" t="n">
-        <v>7057194</v>
+        <v>7057324</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2393,10 +2393,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129751739</v>
+        <v>129751733</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463878</v>
+        <v>463805</v>
       </c>
       <c r="R19" t="n">
-        <v>7057324</v>
+        <v>7057194</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2498,7 +2498,7 @@
         <v>129751735</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>129751711</v>
       </c>
       <c r="B21" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>129751722</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>129751738</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751732</v>
+        <v>129751720</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463782</v>
+        <v>463816</v>
       </c>
       <c r="R24" t="n">
-        <v>7057216</v>
+        <v>7057325</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751720</v>
+        <v>129751732</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463816</v>
+        <v>463782</v>
       </c>
       <c r="R25" t="n">
-        <v>7057325</v>
+        <v>7057216</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3101,7 +3101,7 @@
         <v>129751717</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>129751713</v>
       </c>
       <c r="B27" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>129751716</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>129751731</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751757</v>
+        <v>129751749</v>
       </c>
       <c r="B30" t="n">
-        <v>88998</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,21 +3508,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463874</v>
+        <v>463943</v>
       </c>
       <c r="R30" t="n">
-        <v>7057476</v>
+        <v>7057664</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,6 +3568,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3594,10 +3599,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751749</v>
+        <v>129751714</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463943</v>
+        <v>463852</v>
       </c>
       <c r="R31" t="n">
-        <v>7057664</v>
+        <v>7057546</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3669,7 +3674,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3696,10 +3701,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751714</v>
+        <v>129751757</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>89001</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3707,21 +3712,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3731,10 +3736,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463852</v>
+        <v>463874</v>
       </c>
       <c r="R32" t="n">
-        <v>7057546</v>
+        <v>7057476</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3767,11 +3772,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3801,7 +3801,7 @@
         <v>129751750</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>129751752</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>129751727</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4104,10 +4104,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129751753</v>
+        <v>129751724</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463989</v>
+        <v>463856</v>
       </c>
       <c r="R36" t="n">
-        <v>7057802</v>
+        <v>7057496</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129751745</v>
+        <v>129751753</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463911</v>
+        <v>463989</v>
       </c>
       <c r="R37" t="n">
-        <v>7057496</v>
+        <v>7057802</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4308,10 +4308,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129751724</v>
+        <v>129751745</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463856</v>
+        <v>463911</v>
       </c>
       <c r="R38" t="n">
         <v>7057496</v>
@@ -4410,10 +4410,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129751751</v>
+        <v>129751726</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463918</v>
+        <v>463811</v>
       </c>
       <c r="R39" t="n">
-        <v>7057725</v>
+        <v>7057478</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4512,10 +4512,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129751726</v>
+        <v>129751751</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463811</v>
+        <v>463918</v>
       </c>
       <c r="R40" t="n">
-        <v>7057478</v>
+        <v>7057725</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4617,7 +4617,7 @@
         <v>129751742</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>129751725</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>129751743</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>129751754</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>129751710</v>
       </c>
       <c r="B45" t="n">
-        <v>57840</v>
+        <v>57841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>129751715</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>129751700</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>129751741</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>129751703</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>129751756</v>
       </c>
       <c r="B50" t="n">
-        <v>88998</v>
+        <v>89001</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>129751748</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>129751747</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>129751723</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>129751701</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>129751707</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751730</v>
+        <v>129751699</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1196,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463760</v>
+        <v>463848</v>
       </c>
       <c r="R7" t="n">
-        <v>7057294</v>
+        <v>7057352</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1268,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751712</v>
+        <v>129751730</v>
       </c>
       <c r="B8" t="n">
-        <v>91622</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,19 +1306,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1318,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463850</v>
+        <v>463760</v>
       </c>
       <c r="R8" t="n">
-        <v>7057352</v>
+        <v>7057294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751699</v>
+        <v>129751712</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>91622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,39 +1408,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463848</v>
+        <v>463850</v>
       </c>
       <c r="R9" t="n">
         <v>7057352</v>
@@ -1459,11 +1464,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751709</v>
+        <v>129751705</v>
       </c>
       <c r="B10" t="n">
-        <v>80189</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463921</v>
+        <v>463881</v>
       </c>
       <c r="R10" t="n">
-        <v>7057254</v>
+        <v>7057240</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,6 +1561,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751755</v>
+        <v>129751709</v>
       </c>
       <c r="B11" t="n">
-        <v>89001</v>
+        <v>80189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,21 +1603,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463778</v>
+        <v>463921</v>
       </c>
       <c r="R11" t="n">
-        <v>7057403</v>
+        <v>7057254</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751705</v>
+        <v>129751718</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1719,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463881</v>
+        <v>463790</v>
       </c>
       <c r="R12" t="n">
-        <v>7057240</v>
+        <v>7057272</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1759,7 +1764,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751718</v>
+        <v>129751755</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>89001</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463790</v>
+        <v>463778</v>
       </c>
       <c r="R13" t="n">
-        <v>7057272</v>
+        <v>7057403</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,11 +1862,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -5114,10 +5114,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129751715</v>
+        <v>129751700</v>
       </c>
       <c r="B46" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463874</v>
+        <v>463923</v>
       </c>
       <c r="R46" t="n">
-        <v>7057530</v>
+        <v>7057789</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5216,10 +5216,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129751700</v>
+        <v>129751715</v>
       </c>
       <c r="B47" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5227,21 +5227,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463923</v>
+        <v>463874</v>
       </c>
       <c r="R47" t="n">
-        <v>7057789</v>
+        <v>7057530</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5823,10 +5823,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129751723</v>
+        <v>129751701</v>
       </c>
       <c r="B53" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463838</v>
+        <v>463931</v>
       </c>
       <c r="R53" t="n">
-        <v>7057454</v>
+        <v>7057799</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751701</v>
+        <v>129751723</v>
       </c>
       <c r="B54" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463931</v>
+        <v>463838</v>
       </c>
       <c r="R54" t="n">
-        <v>7057799</v>
+        <v>7057454</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -1592,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751709</v>
+        <v>129751755</v>
       </c>
       <c r="B11" t="n">
-        <v>80189</v>
+        <v>89001</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,21 +1603,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463921</v>
+        <v>463778</v>
       </c>
       <c r="R11" t="n">
-        <v>7057254</v>
+        <v>7057403</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751718</v>
+        <v>129751709</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463790</v>
+        <v>463921</v>
       </c>
       <c r="R12" t="n">
-        <v>7057272</v>
+        <v>7057254</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,11 +1760,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751755</v>
+        <v>129751718</v>
       </c>
       <c r="B13" t="n">
-        <v>89001</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463778</v>
+        <v>463790</v>
       </c>
       <c r="R13" t="n">
-        <v>7057403</v>
+        <v>7057272</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,6 +1857,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751719</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129751740</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129751704</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129751737</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129751728</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751699</v>
+        <v>129751712</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>91625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,39 +1196,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463848</v>
+        <v>463850</v>
       </c>
       <c r="R7" t="n">
         <v>7057352</v>
@@ -1264,11 +1252,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751730</v>
+        <v>129751699</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,34 +1289,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463760</v>
+        <v>463848</v>
       </c>
       <c r="R8" t="n">
-        <v>7057294</v>
+        <v>7057352</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,7 +1361,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751712</v>
+        <v>129751730</v>
       </c>
       <c r="B9" t="n">
-        <v>91622</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,19 +1399,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1428,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463850</v>
+        <v>463760</v>
       </c>
       <c r="R9" t="n">
-        <v>7057352</v>
+        <v>7057294</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,6 +1459,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751705</v>
+        <v>129751755</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>89004</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463881</v>
+        <v>463778</v>
       </c>
       <c r="R10" t="n">
-        <v>7057240</v>
+        <v>7057403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,10 +1587,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751755</v>
+        <v>129751705</v>
       </c>
       <c r="B11" t="n">
-        <v>89001</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,21 +1598,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463778</v>
+        <v>463881</v>
       </c>
       <c r="R11" t="n">
-        <v>7057403</v>
+        <v>7057240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,6 +1658,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751709</v>
+        <v>129751718</v>
       </c>
       <c r="B12" t="n">
-        <v>80189</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463921</v>
+        <v>463790</v>
       </c>
       <c r="R12" t="n">
-        <v>7057254</v>
+        <v>7057272</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,6 +1760,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751718</v>
+        <v>129751709</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>80192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463790</v>
+        <v>463921</v>
       </c>
       <c r="R13" t="n">
-        <v>7057272</v>
+        <v>7057254</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,11 +1862,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,7 +1891,7 @@
         <v>129751734</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>129751729</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129751736</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>129751698</v>
       </c>
       <c r="B17" t="n">
-        <v>92320</v>
+        <v>92323</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>129751739</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129751733</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>129751735</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>129751711</v>
       </c>
       <c r="B21" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>129751722</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>129751738</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>129751720</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>129751732</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>129751717</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129751713</v>
+        <v>129751716</v>
       </c>
       <c r="B27" t="n">
-        <v>91622</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3211,19 +3211,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3231,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463871</v>
+        <v>463820</v>
       </c>
       <c r="R27" t="n">
-        <v>7057401</v>
+        <v>7057388</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3267,6 +3271,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3293,10 +3302,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129751716</v>
+        <v>129751731</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3328,10 +3337,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463820</v>
+        <v>463755</v>
       </c>
       <c r="R28" t="n">
-        <v>7057388</v>
+        <v>7057263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,7 +3377,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3395,10 +3404,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751731</v>
+        <v>129751713</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>91625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,23 +3415,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3430,10 +3435,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463755</v>
+        <v>463871</v>
       </c>
       <c r="R29" t="n">
-        <v>7057263</v>
+        <v>7057401</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3466,11 +3471,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3497,10 +3497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751749</v>
+        <v>129751757</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>89004</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,21 +3508,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463943</v>
+        <v>463874</v>
       </c>
       <c r="R30" t="n">
-        <v>7057664</v>
+        <v>7057476</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,11 +3568,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3599,10 +3594,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751714</v>
+        <v>129751749</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3634,10 +3629,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463852</v>
+        <v>463943</v>
       </c>
       <c r="R31" t="n">
-        <v>7057546</v>
+        <v>7057664</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3674,7 +3669,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3701,10 +3696,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751757</v>
+        <v>129751714</v>
       </c>
       <c r="B32" t="n">
-        <v>89001</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3712,21 +3707,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3736,10 +3731,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463874</v>
+        <v>463852</v>
       </c>
       <c r="R32" t="n">
-        <v>7057476</v>
+        <v>7057546</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,6 +3767,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3801,7 +3801,7 @@
         <v>129751750</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>129751752</v>
       </c>
       <c r="B34" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>129751727</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>129751724</v>
       </c>
       <c r="B36" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129751753</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>129751745</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>129751726</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>129751751</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>129751742</v>
       </c>
       <c r="B41" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>129751725</v>
       </c>
       <c r="B42" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>129751743</v>
       </c>
       <c r="B43" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>129751754</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>129751710</v>
       </c>
       <c r="B45" t="n">
-        <v>57841</v>
+        <v>57844</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>129751700</v>
       </c>
       <c r="B46" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>129751715</v>
       </c>
       <c r="B47" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>129751741</v>
       </c>
       <c r="B48" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>129751703</v>
       </c>
       <c r="B49" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>129751756</v>
       </c>
       <c r="B50" t="n">
-        <v>89001</v>
+        <v>89004</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>129751748</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>129751747</v>
       </c>
       <c r="B52" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>129751701</v>
       </c>
       <c r="B53" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>129751723</v>
       </c>
       <c r="B54" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>129751707</v>
       </c>
       <c r="B55" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751699</v>
+        <v>129751730</v>
       </c>
       <c r="B8" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,42 +1289,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463848</v>
+        <v>463760</v>
       </c>
       <c r="R8" t="n">
-        <v>7057352</v>
+        <v>7057294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,7 +1353,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751730</v>
+        <v>129751699</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,34 +1391,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463760</v>
+        <v>463848</v>
       </c>
       <c r="R9" t="n">
-        <v>7057294</v>
+        <v>7057352</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751755</v>
+        <v>129751705</v>
       </c>
       <c r="B10" t="n">
-        <v>89004</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463778</v>
+        <v>463881</v>
       </c>
       <c r="R10" t="n">
-        <v>7057403</v>
+        <v>7057240</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,6 +1561,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751705</v>
+        <v>129751709</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>80192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,21 +1603,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463881</v>
+        <v>463921</v>
       </c>
       <c r="R11" t="n">
-        <v>7057240</v>
+        <v>7057254</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,11 +1663,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751718</v>
+        <v>129751755</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>89004</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463790</v>
+        <v>463778</v>
       </c>
       <c r="R12" t="n">
-        <v>7057272</v>
+        <v>7057403</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,11 +1760,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751709</v>
+        <v>129751718</v>
       </c>
       <c r="B13" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463921</v>
+        <v>463790</v>
       </c>
       <c r="R13" t="n">
-        <v>7057254</v>
+        <v>7057272</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,6 +1857,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3497,10 +3497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751757</v>
+        <v>129751749</v>
       </c>
       <c r="B30" t="n">
-        <v>89004</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,21 +3508,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463874</v>
+        <v>463943</v>
       </c>
       <c r="R30" t="n">
-        <v>7057476</v>
+        <v>7057664</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,6 +3568,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3594,7 +3599,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751749</v>
+        <v>129751714</v>
       </c>
       <c r="B31" t="n">
         <v>79087</v>
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463943</v>
+        <v>463852</v>
       </c>
       <c r="R31" t="n">
-        <v>7057664</v>
+        <v>7057546</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3669,7 +3674,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3696,10 +3701,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751714</v>
+        <v>129751757</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>89004</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3707,21 +3712,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3731,10 +3736,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463852</v>
+        <v>463874</v>
       </c>
       <c r="R32" t="n">
-        <v>7057546</v>
+        <v>7057476</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3767,11 +3772,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751705</v>
+        <v>129751755</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>89004</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463881</v>
+        <v>463778</v>
       </c>
       <c r="R10" t="n">
-        <v>7057240</v>
+        <v>7057403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,10 +1587,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751709</v>
+        <v>129751705</v>
       </c>
       <c r="B11" t="n">
-        <v>80192</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,21 +1598,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463921</v>
+        <v>463881</v>
       </c>
       <c r="R11" t="n">
-        <v>7057254</v>
+        <v>7057240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,6 +1658,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751755</v>
+        <v>129751718</v>
       </c>
       <c r="B12" t="n">
-        <v>89004</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463778</v>
+        <v>463790</v>
       </c>
       <c r="R12" t="n">
-        <v>7057403</v>
+        <v>7057272</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,6 +1760,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751718</v>
+        <v>129751709</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>80192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463790</v>
+        <v>463921</v>
       </c>
       <c r="R13" t="n">
-        <v>7057272</v>
+        <v>7057254</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,11 +1862,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751719</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129751740</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129751737</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129751728</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>129751712</v>
       </c>
       <c r="B7" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>129751730</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751755</v>
+        <v>129751718</v>
       </c>
       <c r="B10" t="n">
-        <v>89004</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463778</v>
+        <v>463790</v>
       </c>
       <c r="R10" t="n">
-        <v>7057403</v>
+        <v>7057272</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,6 +1561,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751705</v>
+        <v>129751755</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>89005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,21 +1603,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463881</v>
+        <v>463778</v>
       </c>
       <c r="R11" t="n">
-        <v>7057240</v>
+        <v>7057403</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,11 +1663,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751718</v>
+        <v>129751705</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463790</v>
+        <v>463881</v>
       </c>
       <c r="R12" t="n">
-        <v>7057272</v>
+        <v>7057240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1794,7 +1794,7 @@
         <v>129751709</v>
       </c>
       <c r="B13" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>129751734</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>129751729</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129751736</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>129751698</v>
       </c>
       <c r="B17" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>129751739</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129751733</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>129751735</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>129751711</v>
       </c>
       <c r="B21" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>129751722</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>129751738</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751720</v>
+        <v>129751732</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463816</v>
+        <v>463782</v>
       </c>
       <c r="R24" t="n">
-        <v>7057325</v>
+        <v>7057216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751732</v>
+        <v>129751720</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463782</v>
+        <v>463816</v>
       </c>
       <c r="R25" t="n">
-        <v>7057216</v>
+        <v>7057325</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3101,7 +3101,7 @@
         <v>129751717</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129751716</v>
+        <v>129751713</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>91626</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3211,23 +3211,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3235,10 +3231,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463820</v>
+        <v>463871</v>
       </c>
       <c r="R27" t="n">
-        <v>7057388</v>
+        <v>7057401</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3271,11 +3267,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3305,7 +3296,7 @@
         <v>129751731</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3404,10 +3395,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751713</v>
+        <v>129751716</v>
       </c>
       <c r="B29" t="n">
-        <v>91625</v>
+        <v>79088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,19 +3406,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3435,10 +3430,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463871</v>
+        <v>463820</v>
       </c>
       <c r="R29" t="n">
-        <v>7057401</v>
+        <v>7057388</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3471,6 +3466,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3497,10 +3497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751749</v>
+        <v>129751714</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463943</v>
+        <v>463852</v>
       </c>
       <c r="R30" t="n">
-        <v>7057664</v>
+        <v>7057546</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3599,10 +3599,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751714</v>
+        <v>129751757</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>89005</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463852</v>
+        <v>463874</v>
       </c>
       <c r="R31" t="n">
-        <v>7057546</v>
+        <v>7057476</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3670,11 +3670,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3701,10 +3696,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751757</v>
+        <v>129751749</v>
       </c>
       <c r="B32" t="n">
-        <v>89004</v>
+        <v>79088</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3712,21 +3707,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3736,10 +3731,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463874</v>
+        <v>463943</v>
       </c>
       <c r="R32" t="n">
-        <v>7057476</v>
+        <v>7057664</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,6 +3767,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3801,7 +3801,7 @@
         <v>129751750</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>129751752</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>129751727</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>129751724</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4206,10 +4206,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129751753</v>
+        <v>129751745</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463989</v>
+        <v>463911</v>
       </c>
       <c r="R37" t="n">
-        <v>7057802</v>
+        <v>7057496</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4308,10 +4308,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129751745</v>
+        <v>129751753</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463911</v>
+        <v>463989</v>
       </c>
       <c r="R38" t="n">
-        <v>7057496</v>
+        <v>7057802</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4413,7 +4413,7 @@
         <v>129751726</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>129751751</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>129751742</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>129751725</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>129751743</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>129751754</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129751700</v>
+        <v>129751715</v>
       </c>
       <c r="B46" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463923</v>
+        <v>463874</v>
       </c>
       <c r="R46" t="n">
-        <v>7057789</v>
+        <v>7057530</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5216,10 +5216,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129751715</v>
+        <v>129751700</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5227,21 +5227,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463874</v>
+        <v>463923</v>
       </c>
       <c r="R47" t="n">
-        <v>7057530</v>
+        <v>7057789</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5321,7 +5321,7 @@
         <v>129751741</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>129751756</v>
       </c>
       <c r="B50" t="n">
-        <v>89004</v>
+        <v>89005</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>129751748</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>129751747</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>129751723</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -4104,7 +4104,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129751724</v>
+        <v>129751753</v>
       </c>
       <c r="B36" t="n">
         <v>79088</v>
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463856</v>
+        <v>463989</v>
       </c>
       <c r="R36" t="n">
-        <v>7057496</v>
+        <v>7057802</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4206,7 +4206,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129751745</v>
+        <v>129751724</v>
       </c>
       <c r="B37" t="n">
         <v>79088</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463911</v>
+        <v>463856</v>
       </c>
       <c r="R37" t="n">
         <v>7057496</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129751753</v>
+        <v>129751745</v>
       </c>
       <c r="B38" t="n">
         <v>79088</v>
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463989</v>
+        <v>463911</v>
       </c>
       <c r="R38" t="n">
-        <v>7057802</v>
+        <v>7057496</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751719</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129751740</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129751737</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129751728</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>129751712</v>
       </c>
       <c r="B7" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>129751730</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751718</v>
+        <v>129751755</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>89022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463790</v>
+        <v>463778</v>
       </c>
       <c r="R10" t="n">
-        <v>7057272</v>
+        <v>7057403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,10 +1587,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751755</v>
+        <v>129751718</v>
       </c>
       <c r="B11" t="n">
-        <v>89005</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,21 +1598,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463778</v>
+        <v>463790</v>
       </c>
       <c r="R11" t="n">
-        <v>7057403</v>
+        <v>7057272</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,6 +1658,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,7 +1794,7 @@
         <v>129751709</v>
       </c>
       <c r="B13" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>129751734</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>129751729</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129751736</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>129751698</v>
       </c>
       <c r="B17" t="n">
-        <v>92324</v>
+        <v>92341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>129751739</v>
       </c>
       <c r="B18" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129751733</v>
       </c>
       <c r="B19" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>129751735</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>129751711</v>
       </c>
       <c r="B21" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>129751722</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>129751738</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751732</v>
+        <v>129751720</v>
       </c>
       <c r="B24" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463782</v>
+        <v>463816</v>
       </c>
       <c r="R24" t="n">
-        <v>7057216</v>
+        <v>7057325</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751720</v>
+        <v>129751732</v>
       </c>
       <c r="B25" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463816</v>
+        <v>463782</v>
       </c>
       <c r="R25" t="n">
-        <v>7057325</v>
+        <v>7057216</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3101,7 +3101,7 @@
         <v>129751717</v>
       </c>
       <c r="B26" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>129751713</v>
       </c>
       <c r="B27" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3293,10 +3293,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129751731</v>
+        <v>129751716</v>
       </c>
       <c r="B28" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463755</v>
+        <v>463820</v>
       </c>
       <c r="R28" t="n">
-        <v>7057263</v>
+        <v>7057388</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3395,10 +3395,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751716</v>
+        <v>129751731</v>
       </c>
       <c r="B29" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463820</v>
+        <v>463755</v>
       </c>
       <c r="R29" t="n">
-        <v>7057388</v>
+        <v>7057263</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3497,10 +3497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751714</v>
+        <v>129751749</v>
       </c>
       <c r="B30" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463852</v>
+        <v>463943</v>
       </c>
       <c r="R30" t="n">
-        <v>7057546</v>
+        <v>7057664</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3599,10 +3599,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751757</v>
+        <v>129751714</v>
       </c>
       <c r="B31" t="n">
-        <v>89005</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463874</v>
+        <v>463852</v>
       </c>
       <c r="R31" t="n">
-        <v>7057476</v>
+        <v>7057546</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3670,6 +3670,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3696,10 +3701,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751749</v>
+        <v>129751757</v>
       </c>
       <c r="B32" t="n">
-        <v>79088</v>
+        <v>89022</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3707,21 +3712,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3731,10 +3736,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463943</v>
+        <v>463874</v>
       </c>
       <c r="R32" t="n">
-        <v>7057664</v>
+        <v>7057476</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3767,11 +3772,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3801,7 +3801,7 @@
         <v>129751750</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>129751752</v>
       </c>
       <c r="B34" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>129751727</v>
       </c>
       <c r="B35" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4104,10 +4104,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129751753</v>
+        <v>129751724</v>
       </c>
       <c r="B36" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463989</v>
+        <v>463856</v>
       </c>
       <c r="R36" t="n">
-        <v>7057802</v>
+        <v>7057496</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129751724</v>
+        <v>129751753</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463856</v>
+        <v>463989</v>
       </c>
       <c r="R37" t="n">
-        <v>7057496</v>
+        <v>7057802</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4311,7 +4311,7 @@
         <v>129751745</v>
       </c>
       <c r="B38" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>129751726</v>
       </c>
       <c r="B39" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>129751751</v>
       </c>
       <c r="B40" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>129751742</v>
       </c>
       <c r="B41" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>129751725</v>
       </c>
       <c r="B42" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>129751743</v>
       </c>
       <c r="B43" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>129751754</v>
       </c>
       <c r="B44" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>129751715</v>
       </c>
       <c r="B46" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>129751741</v>
       </c>
       <c r="B48" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>129751756</v>
       </c>
       <c r="B50" t="n">
-        <v>89005</v>
+        <v>89022</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>129751748</v>
       </c>
       <c r="B51" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>129751747</v>
       </c>
       <c r="B52" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5823,10 +5823,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129751701</v>
+        <v>129751723</v>
       </c>
       <c r="B53" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463931</v>
+        <v>463838</v>
       </c>
       <c r="R53" t="n">
-        <v>7057799</v>
+        <v>7057454</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751723</v>
+        <v>129751701</v>
       </c>
       <c r="B54" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463838</v>
+        <v>463931</v>
       </c>
       <c r="R54" t="n">
-        <v>7057454</v>
+        <v>7057799</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129751719</v>
+        <v>129751755</v>
       </c>
       <c r="B2" t="n">
-        <v>79094</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463828</v>
+        <v>463778</v>
       </c>
       <c r="R2" t="n">
-        <v>7057254</v>
+        <v>7057403</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751740</v>
+        <v>129751756</v>
       </c>
       <c r="B3" t="n">
-        <v>79094</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463870</v>
+        <v>463888</v>
       </c>
       <c r="R3" t="n">
-        <v>7057365</v>
+        <v>7057449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751704</v>
+        <v>129751757</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463758</v>
+        <v>463874</v>
       </c>
       <c r="R4" t="n">
-        <v>7057263</v>
+        <v>7057476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129751737</v>
+        <v>129751708</v>
       </c>
       <c r="B5" t="n">
-        <v>79094</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463938</v>
+        <v>463941</v>
       </c>
       <c r="R5" t="n">
-        <v>7057280</v>
+        <v>7057566</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129751728</v>
+        <v>129751697</v>
       </c>
       <c r="B6" t="n">
-        <v>79094</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463783</v>
+        <v>463941</v>
       </c>
       <c r="R6" t="n">
-        <v>7057398</v>
+        <v>7057566</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751730</v>
+        <v>129751698</v>
       </c>
       <c r="B7" t="n">
-        <v>79094</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463760</v>
+        <v>463895</v>
       </c>
       <c r="R7" t="n">
-        <v>7057294</v>
+        <v>7057304</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,30 +1257,34 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751712</v>
+        <v>129751714</v>
       </c>
       <c r="B8" t="n">
-        <v>91658</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1318,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463850</v>
+        <v>463852</v>
       </c>
       <c r="R8" t="n">
-        <v>7057352</v>
+        <v>7057546</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,6 +1328,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,53 +1359,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751699</v>
+        <v>129751715</v>
       </c>
       <c r="B9" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463848</v>
+        <v>463874</v>
       </c>
       <c r="R9" t="n">
-        <v>7057352</v>
+        <v>7057530</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,7 +1434,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,14 +1461,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751718</v>
+        <v>129751716</v>
       </c>
       <c r="B10" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1525,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463790</v>
+        <v>463820</v>
       </c>
       <c r="R10" t="n">
-        <v>7057272</v>
+        <v>7057388</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751709</v>
+        <v>129751717</v>
       </c>
       <c r="B11" t="n">
-        <v>80199</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463921</v>
+        <v>463782</v>
       </c>
       <c r="R11" t="n">
-        <v>7057254</v>
+        <v>7057309</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,6 +1634,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,32 +1665,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751705</v>
+        <v>129751718</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463881</v>
+        <v>463790</v>
       </c>
       <c r="R12" t="n">
-        <v>7057240</v>
+        <v>7057272</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1764,7 +1740,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,32 +1767,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751755</v>
+        <v>129751719</v>
       </c>
       <c r="B13" t="n">
-        <v>89037</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463778</v>
+        <v>463828</v>
       </c>
       <c r="R13" t="n">
-        <v>7057403</v>
+        <v>7057254</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,6 +1838,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1888,14 +1869,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129751734</v>
+        <v>129751720</v>
       </c>
       <c r="B14" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1923,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463845</v>
+        <v>463816</v>
       </c>
       <c r="R14" t="n">
-        <v>7057198</v>
+        <v>7057325</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,14 +1971,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129751729</v>
+        <v>129751722</v>
       </c>
       <c r="B15" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2025,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463781</v>
+        <v>463804</v>
       </c>
       <c r="R15" t="n">
-        <v>7057385</v>
+        <v>7057362</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,7 +2046,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2092,14 +2073,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751736</v>
+        <v>129751723</v>
       </c>
       <c r="B16" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2127,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463912</v>
+        <v>463838</v>
       </c>
       <c r="R16" t="n">
-        <v>7057247</v>
+        <v>7057454</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,32 +2175,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751698</v>
+        <v>129751724</v>
       </c>
       <c r="B17" t="n">
-        <v>92356</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2229,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463895</v>
+        <v>463856</v>
       </c>
       <c r="R17" t="n">
-        <v>7057304</v>
+        <v>7057496</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,6 +2246,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2291,14 +2277,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129751735</v>
+        <v>129751725</v>
       </c>
       <c r="B18" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2326,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463867</v>
+        <v>463827</v>
       </c>
       <c r="R18" t="n">
-        <v>7057230</v>
+        <v>7057498</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,14 +2379,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129751739</v>
+        <v>129751726</v>
       </c>
       <c r="B19" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2428,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463878</v>
+        <v>463811</v>
       </c>
       <c r="R19" t="n">
-        <v>7057324</v>
+        <v>7057478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2468,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2495,14 +2481,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129751733</v>
+        <v>129751727</v>
       </c>
       <c r="B20" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2530,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463805</v>
+        <v>463777</v>
       </c>
       <c r="R20" t="n">
-        <v>7057194</v>
+        <v>7057457</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2597,30 +2583,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751711</v>
+        <v>129751728</v>
       </c>
       <c r="B21" t="n">
-        <v>91658</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2628,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463790</v>
+        <v>463783</v>
       </c>
       <c r="R21" t="n">
-        <v>7057363</v>
+        <v>7057398</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,6 +2654,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,14 +2685,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129751722</v>
+        <v>129751729</v>
       </c>
       <c r="B22" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2725,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463804</v>
+        <v>463781</v>
       </c>
       <c r="R22" t="n">
-        <v>7057362</v>
+        <v>7057385</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2765,7 +2760,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2792,14 +2787,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129751738</v>
+        <v>129751730</v>
       </c>
       <c r="B23" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2827,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463940</v>
+        <v>463760</v>
       </c>
       <c r="R23" t="n">
-        <v>7057328</v>
+        <v>7057294</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2867,7 +2862,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2894,14 +2889,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751720</v>
+        <v>129751731</v>
       </c>
       <c r="B24" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2929,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463816</v>
+        <v>463755</v>
       </c>
       <c r="R24" t="n">
-        <v>7057325</v>
+        <v>7057263</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2969,7 +2964,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2999,11 +2994,11 @@
         <v>129751732</v>
       </c>
       <c r="B25" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3098,14 +3093,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129751717</v>
+        <v>129751733</v>
       </c>
       <c r="B26" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3133,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>463782</v>
+        <v>463805</v>
       </c>
       <c r="R26" t="n">
-        <v>7057309</v>
+        <v>7057194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3200,30 +3195,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129751713</v>
+        <v>129751734</v>
       </c>
       <c r="B27" t="n">
-        <v>91658</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3231,10 +3230,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463871</v>
+        <v>463845</v>
       </c>
       <c r="R27" t="n">
-        <v>7057401</v>
+        <v>7057198</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3267,6 +3266,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3293,14 +3297,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129751716</v>
+        <v>129751735</v>
       </c>
       <c r="B28" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3328,10 +3332,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463820</v>
+        <v>463867</v>
       </c>
       <c r="R28" t="n">
-        <v>7057388</v>
+        <v>7057230</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3395,14 +3399,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751731</v>
+        <v>129751736</v>
       </c>
       <c r="B29" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3430,10 +3434,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463755</v>
+        <v>463912</v>
       </c>
       <c r="R29" t="n">
-        <v>7057263</v>
+        <v>7057247</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,7 +3474,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3497,32 +3501,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751757</v>
+        <v>129751737</v>
       </c>
       <c r="B30" t="n">
-        <v>89037</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3532,10 +3536,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463874</v>
+        <v>463938</v>
       </c>
       <c r="R30" t="n">
-        <v>7057476</v>
+        <v>7057280</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,6 +3572,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3594,14 +3603,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751714</v>
+        <v>129751738</v>
       </c>
       <c r="B31" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3629,10 +3638,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463852</v>
+        <v>463940</v>
       </c>
       <c r="R31" t="n">
-        <v>7057546</v>
+        <v>7057328</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3669,7 +3678,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3696,14 +3705,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751749</v>
+        <v>129751739</v>
       </c>
       <c r="B32" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3731,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463943</v>
+        <v>463878</v>
       </c>
       <c r="R32" t="n">
-        <v>7057664</v>
+        <v>7057324</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3798,14 +3807,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129751750</v>
+        <v>129751740</v>
       </c>
       <c r="B33" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3833,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463927</v>
+        <v>463870</v>
       </c>
       <c r="R33" t="n">
-        <v>7057682</v>
+        <v>7057365</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3900,14 +3909,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129751752</v>
+        <v>129751741</v>
       </c>
       <c r="B34" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3935,10 +3944,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463921</v>
+        <v>463860</v>
       </c>
       <c r="R34" t="n">
-        <v>7057766</v>
+        <v>7057447</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3975,7 +3984,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4002,14 +4011,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129751727</v>
+        <v>129751742</v>
       </c>
       <c r="B35" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4037,10 +4046,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463777</v>
+        <v>463882</v>
       </c>
       <c r="R35" t="n">
-        <v>7057457</v>
+        <v>7057443</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4077,7 +4086,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4104,14 +4113,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129751724</v>
+        <v>129751743</v>
       </c>
       <c r="B36" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4139,10 +4148,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463856</v>
+        <v>463870</v>
       </c>
       <c r="R36" t="n">
-        <v>7057496</v>
+        <v>7057473</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,7 +4188,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4206,14 +4215,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129751753</v>
+        <v>129751745</v>
       </c>
       <c r="B37" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4241,10 +4250,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463989</v>
+        <v>463911</v>
       </c>
       <c r="R37" t="n">
-        <v>7057802</v>
+        <v>7057496</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4281,7 +4290,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4308,14 +4317,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129751745</v>
+        <v>129751747</v>
       </c>
       <c r="B38" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4343,10 +4352,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463911</v>
+        <v>463926</v>
       </c>
       <c r="R38" t="n">
-        <v>7057496</v>
+        <v>7057553</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4410,14 +4419,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129751726</v>
+        <v>129751748</v>
       </c>
       <c r="B39" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4445,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463811</v>
+        <v>463928</v>
       </c>
       <c r="R39" t="n">
-        <v>7057478</v>
+        <v>7057569</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4485,7 +4494,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4512,14 +4521,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129751751</v>
+        <v>129751749</v>
       </c>
       <c r="B40" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4547,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463918</v>
+        <v>463943</v>
       </c>
       <c r="R40" t="n">
-        <v>7057725</v>
+        <v>7057664</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4614,14 +4623,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129751742</v>
+        <v>129751750</v>
       </c>
       <c r="B41" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4649,10 +4658,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>463882</v>
+        <v>463927</v>
       </c>
       <c r="R41" t="n">
-        <v>7057443</v>
+        <v>7057682</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,7 +4698,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4716,14 +4725,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129751725</v>
+        <v>129751751</v>
       </c>
       <c r="B42" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4751,10 +4760,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>463827</v>
+        <v>463918</v>
       </c>
       <c r="R42" t="n">
-        <v>7057498</v>
+        <v>7057725</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,7 +4800,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4818,14 +4827,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129751743</v>
+        <v>129751752</v>
       </c>
       <c r="B43" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4853,10 +4862,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463870</v>
+        <v>463921</v>
       </c>
       <c r="R43" t="n">
-        <v>7057473</v>
+        <v>7057766</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4920,14 +4929,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129751754</v>
+        <v>129751753</v>
       </c>
       <c r="B44" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4955,10 +4964,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464011</v>
+        <v>463989</v>
       </c>
       <c r="R44" t="n">
-        <v>7057803</v>
+        <v>7057802</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4991,6 +5000,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5017,32 +5031,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129751710</v>
+        <v>129751754</v>
       </c>
       <c r="B45" t="n">
-        <v>57844</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5052,10 +5066,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>463833</v>
+        <v>464011</v>
       </c>
       <c r="R45" t="n">
-        <v>7057477</v>
+        <v>7057803</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5114,10 +5128,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129751715</v>
+        <v>129751709</v>
       </c>
       <c r="B46" t="n">
-        <v>79094</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,21 +5139,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5149,10 +5163,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463874</v>
+        <v>463921</v>
       </c>
       <c r="R46" t="n">
-        <v>7057530</v>
+        <v>7057254</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5185,11 +5199,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5216,10 +5225,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129751700</v>
+        <v>129751699</v>
       </c>
       <c r="B47" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,16 +5254,24 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjockmjölkbodhön N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463923</v>
+        <v>463848</v>
       </c>
       <c r="R47" t="n">
-        <v>7057789</v>
+        <v>7057352</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,7 +5308,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Gammalt bohål, troligtvis tidigare tillhörande tretåig hackspett,  ca 1,7m upp i grantickeröta o bruten gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5318,10 +5335,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129751741</v>
+        <v>129751700</v>
       </c>
       <c r="B48" t="n">
-        <v>79094</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5329,21 +5346,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5353,10 +5370,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>463860</v>
+        <v>463923</v>
       </c>
       <c r="R48" t="n">
-        <v>7057447</v>
+        <v>7057789</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5393,7 +5410,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5420,10 +5437,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129751703</v>
+        <v>129751701</v>
       </c>
       <c r="B49" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5455,10 +5472,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>463886</v>
+        <v>463931</v>
       </c>
       <c r="R49" t="n">
-        <v>7057558</v>
+        <v>7057799</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5522,10 +5539,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129751756</v>
+        <v>129751703</v>
       </c>
       <c r="B50" t="n">
-        <v>89037</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5533,21 +5550,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5557,10 +5574,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>463888</v>
+        <v>463886</v>
       </c>
       <c r="R50" t="n">
-        <v>7057449</v>
+        <v>7057558</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5593,6 +5610,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5619,10 +5641,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129751748</v>
+        <v>129751704</v>
       </c>
       <c r="B51" t="n">
-        <v>79094</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5630,21 +5652,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5654,10 +5676,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>463928</v>
+        <v>463758</v>
       </c>
       <c r="R51" t="n">
-        <v>7057569</v>
+        <v>7057263</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5694,7 +5716,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5721,10 +5743,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129751747</v>
+        <v>129751705</v>
       </c>
       <c r="B52" t="n">
-        <v>79094</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5732,21 +5754,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5756,10 +5778,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>463926</v>
+        <v>463881</v>
       </c>
       <c r="R52" t="n">
-        <v>7057553</v>
+        <v>7057240</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5796,7 +5818,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5823,10 +5845,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129751723</v>
+        <v>129751706</v>
       </c>
       <c r="B53" t="n">
-        <v>79094</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5834,21 +5856,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5858,10 +5880,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463838</v>
+        <v>463902</v>
       </c>
       <c r="R53" t="n">
-        <v>7057454</v>
+        <v>7057704</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5920,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5947,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751701</v>
+        <v>129751707</v>
       </c>
       <c r="B54" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5960,10 +5982,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463931</v>
+        <v>463932</v>
       </c>
       <c r="R54" t="n">
-        <v>7057799</v>
+        <v>7057762</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6027,10 +6049,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129751707</v>
+        <v>129751710</v>
       </c>
       <c r="B55" t="n">
-        <v>57740</v>
+        <v>58057</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6038,16 +6060,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6062,10 +6084,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>463932</v>
+        <v>463833</v>
       </c>
       <c r="R55" t="n">
-        <v>7057762</v>
+        <v>7057477</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6098,11 +6120,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 50196-2025 artfynd.xlsx
+++ b/artfynd/A 50196-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751755</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751756</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751757</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751708</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751697</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751698</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751714</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751715</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751716</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751717</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751718</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751719</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751720</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751722</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751723</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2274,6 +2354,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751724</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2376,6 +2461,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751725</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751726</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2580,6 +2675,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751727</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2682,6 +2782,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751728</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2784,6 +2889,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751729</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2886,6 +2996,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751730</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2988,6 +3103,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751731</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3090,6 +3210,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751732</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3192,6 +3317,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751733</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3294,6 +3424,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751734</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3396,6 +3531,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751735</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3498,6 +3638,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751736</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3600,6 +3745,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751737</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3702,6 +3852,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751738</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3804,6 +3959,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751739</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3906,6 +4066,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751740</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4008,6 +4173,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751741</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4110,6 +4280,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751742</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4212,6 +4387,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751743</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4314,6 +4494,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751745</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4416,6 +4601,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751747</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4518,6 +4708,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751748</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4620,6 +4815,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751749</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4722,6 +4922,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751750</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4824,6 +5029,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751751</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4926,6 +5136,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751752</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5028,6 +5243,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751753</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5125,6 +5345,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751754</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5222,6 +5447,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751709</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5332,6 +5562,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751699</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5434,6 +5669,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751700</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5536,6 +5776,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751701</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5638,6 +5883,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751703</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5740,6 +5990,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751704</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5842,6 +6097,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751705</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5944,6 +6204,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751706</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6046,6 +6311,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751707</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6143,8 +6413,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751710</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>